--- a/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pneumatica industriale, compressori, stazioni di compressione, utensili pneumatici (Festo, SMC, Camozzi, AZ); attiva su tutta la Dalmazia</t>
+          <t>Pneumatica industriale, compressori, stazioni di compressione, utensili pneumatici (Festo, SMC, Camozzi, AZ); attiva su tutta la Dalmazia [DUPLICATO — vedi anche: 2026-09-16_04_Croazia_Zadarska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -573,8 +573,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Gas tecnici e attrezzature per saldatura/taglio; presenza a Zadar confermata, contatti diretti della filiale non reperiti pubblicamente</t>
@@ -612,7 +610,6 @@
           <t>023 251 449</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Rivenditore/importatore utensili industriali (Makita, Metabo, Bosch, DeWalt, Stanley, Unior, Knipex), saldatura, macchine di taglio/piegatura, DPI</t>
@@ -714,7 +711,6 @@
           <t>Primat, trgovački obrt, vl. Šime Peša</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Zaton, Nin (Zadarska županija)</t>
@@ -730,7 +726,6 @@
           <t>023 265 800</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Piccolo obrt (ditta individuale) di ferramenta, utensili, forniture per officine</t>
@@ -748,7 +743,6 @@
           <t>Alan-Trade d.o.o.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Zadar (Murvica 8)</t>
@@ -764,7 +758,6 @@
           <t>023 276 197</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Presente in directory commerciali come rivenditore di utensili e macchine utensili; nessun sito ufficiale/registro camerale dettagliato reperito, verifica ulteriore consigliata</t>

--- a/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gas tecnici e attrezzature per saldatura/taglio; presenza a Zadar confermata, contatti diretti della filiale non reperiti pubblicamente</t>
+          <t>Gas tecnici e attrezzature per saldatura/taglio; presenza a Zadar confermata, contatti diretti della filiale non reperiti pubblicamente [DUPLICATO — vedi anche: 2026-09-08_23_Croazia_Sisacko-moslavacka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
